--- a/exports/게이트C_합성시뮬응답_v1.5_3차.xlsx
+++ b/exports/게이트C_합성시뮬응답_v1.5_3차.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Y51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,7 +554,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>35-39</t>
+          <t>40+</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -564,12 +564,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1인가구</t>
+          <t>2인가구</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6+회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -579,30 +579,30 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>①향신료향 부담</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>향신료 부담 없음</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>5분 완조리</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>외식 대비 가성비</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>가격 걱정</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>배달·외식</t>
+          <t>직접 만든다</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -642,12 +642,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>가(T1·완성도)</t>
+          <t>나(T2·매실청)</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>혼자 살아서 5분이면 되는 게 제일 크죠</t>
+          <t>고수 부담 없다는 거 하나는 끌리네요 (나머진 글쎄)</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>직장인 커뮤니티</t>
+          <t>지인 소개</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35-39</t>
+          <t>40+</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>6+회</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>있다</t>
+          <t>없다</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>⑥지금도 잘 먹음</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -715,17 +715,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>매실청의 새콤한 맛</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -735,27 +735,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>이런 맛 안 찾음</t>
+          <t>배달·외식</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>가끔 산다</t>
+          <t>기존 방식 유지</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>나(T2·매실청)</t>
+          <t>가(T1·완성도)</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>고수 부담 없다는 게 딱 내 얘기라서</t>
+          <t>팟타이 좋아해서 사먹곤 했는데 집에서 5분이면 딱이라</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25-29</t>
+          <t>40+</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0회</t>
+          <t>1-2회</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -843,12 +843,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>국산 새우·숙주 등 재료</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>냉동/밀키트</t>
+          <t>직접 만든다</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>기존 방식 유지</t>
+          <t>가끔 산다</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -888,13 +888,13 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>나(T2·매실청)</t>
+          <t>가(T1·완성도)</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>확장세그</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>35-39</t>
+          <t>40+</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>없다</t>
+          <t>있다</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -949,25 +949,25 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>①향신료향 부담</t>
+          <t>⑥지금도 잘 먹음</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>국산 새우·숙주 등 재료</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>진짜 팟타이 아닐 것</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>배달·외식</t>
+          <t>안 먹거나 참는다</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>꼭 산다</t>
+          <t>기존 방식 유지</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>나(T2·매실청)</t>
+          <t>가(T1·완성도)</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>직장인 커뮤니티</t>
+          <t>지인 소개</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>35-39</t>
+          <t>25-29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1058,45 +1058,45 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>없다</t>
+          <t>있다</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>①향신료향 부담</t>
+          <t>③접근성 부족</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>외식 대비 가성비</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>그렇다</t>
+          <t>아니다</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>이런 맛 안 찾음</t>
+          <t>배달·외식</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>30-34</t>
+          <t>25-29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3-5회</t>
+          <t>1-2회</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1182,16 +1182,16 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>먹어봤고 좋아한다</t>
+          <t>먹어봤고 보통이다</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>⑥지금도 잘 먹음</t>
+          <t>④가격 부담</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>가끔 산다</t>
+          <t>기존 방식 유지</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>매실청으로 새콤함 잡았다는데 진짜 팟타이 맛일지 궁금</t>
+          <t>매실청으로 바꿨다는데 진짜 그 맛 날지 반신반의라</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>35-39</t>
+          <t>25-29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>직장인</t>
+          <t>대학원생</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>없다</t>
+          <t>있다</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>①향신료향 부담</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1318,17 +1318,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>향신료 부담 없음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>매실청의 새콤한 맛</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>양(300g) 부족</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>냉동/밀키트</t>
+          <t>직접 만든다</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1368,10 +1368,14 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>가(T1·완성도)</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
+          <t>나(T2·매실청)</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>고수 부담 없다는 게 딱 내 얘기라</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>기타</t>
@@ -1394,12 +1398,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>직장인 커뮤니티</t>
+          <t>지인 소개</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19-24</t>
+          <t>40+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1414,7 +1418,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1424,7 +1428,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1433,21 +1437,21 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>매실청의 새콤한 맛</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>국산 새우·숙주 등 재료</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1457,7 +1461,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>이런 맛 안 찾음</t>
+          <t>직접 만든다</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1493,7 +1497,7 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>확장세그</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1513,12 +1517,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>직장인 커뮤니티</t>
+          <t>지인 소개</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>35-39</t>
+          <t>30-34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1528,27 +1532,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1인가구</t>
+          <t>가족거주</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6+회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>있다</t>
+          <t>없다</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>먹어봤고 좋아한다</t>
+          <t>먹어봤고 보통이다</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>①향신료향 부담</t>
+          <t>③접근성 부족</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1556,17 +1560,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>국산 새우·숙주 등 재료</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1576,22 +1580,22 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>냉동/밀키트</t>
+          <t>안 먹거나 참는다</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>가끔 산다</t>
+          <t>기존 방식 유지</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1612,12 +1616,12 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>타깃</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1637,7 +1641,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>35-39</t>
+          <t>25-29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1647,12 +1651,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>6+회</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1662,7 +1666,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1671,7 +1675,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1680,12 +1684,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>매실청의 새콤한 맛</t>
+          <t>국산 새우·숙주 등 재료</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1695,27 +1699,27 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>안 먹거나 참는다</t>
+          <t>배달·외식</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>가끔 산다</t>
+          <t>기존 방식 유지</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1731,12 +1735,12 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1751,12 +1755,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>직장인 커뮤니티</t>
+          <t>지인 소개</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>30-34</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1771,17 +1775,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6+회</t>
+          <t>1-2회</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>없다</t>
+          <t>있다</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1790,7 +1794,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1799,12 +1803,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>매실청의 새콤한 맛</t>
+          <t>외식 대비 가성비</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>양(300g) 부족</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1814,22 +1818,22 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>배달·외식</t>
+          <t>냉동/밀키트</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>가끔 산다</t>
+          <t>꼭 산다</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1870,17 +1874,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>직장인 커뮤니티</t>
+          <t>지인 소개</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>30-34</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>직장인</t>
+          <t>자영업·프리랜서</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1890,7 +1894,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>0회</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1909,7 +1913,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1923,7 +1927,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>진짜 팟타이 아닐 것</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1933,32 +1937,32 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>배달·외식</t>
+          <t>안 먹거나 참는다</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>기존 방식 유지</t>
+          <t>가끔 산다</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1968,17 +1972,17 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>진짜 팟타이 맛일지 그게 걱정이었는데 딱 그 부분 짚어줘서</t>
+          <t>매실청 새콤한 맛이 어떨지 궁금해서요</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>타깃</t>
+          <t>확장세그</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1993,7 +1997,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>지인 소개</t>
+          <t>직장인 커뮤니티</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2008,12 +2012,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3-5회</t>
+          <t>6+회</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2032,7 +2036,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2046,7 +2050,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>진짜 팟타이 아닐 것</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2056,7 +2060,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>배달·외식</t>
+          <t>냉동/밀키트</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2066,7 +2070,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2086,18 +2090,18 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>나(T2·매실청)</t>
+          <t>가(T1·완성도)</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2112,42 +2116,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>직장인 커뮤니티</t>
+          <t>지인 소개</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>25-29</t>
+          <t>30-34</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>직장인</t>
+          <t>자영업·프리랜서</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0회</t>
+          <t>6+회</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>있다</t>
+          <t>없다</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>①향신료향 부담</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2160,12 +2164,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>외식 대비 가성비</t>
+          <t>매실청의 새콤한 맛</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2195,28 +2199,32 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>가(T1·완성도)</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr"/>
+          <t>나(T2·매실청)</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>매실청이라 향 부담도 없고 진짜 팟타이 맛일지 궁금</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>확장세그</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2236,7 +2244,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25-29</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2251,12 +2259,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6+회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>있다</t>
+          <t>없다</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2266,11 +2274,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>⑥지금도 잘 먹음</t>
+          <t>③접근성 부족</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2279,12 +2287,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>국산 새우·숙주 등 재료</t>
+          <t>향신료 부담 없음</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2309,7 +2317,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2327,11 +2335,7 @@
           <t>가(T1·완성도)</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>배달로 시켜먹던 건데 집에서 5분이면 되니까 ㅇㅇ</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>타깃</t>
@@ -2359,7 +2363,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19-24</t>
+          <t>25-29</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2384,27 +2388,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>먹어봤고 좋아한다</t>
+          <t>먹어봤고 보통이다</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>⑥지금도 잘 먹음</t>
+          <t>①향신료향 부담</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>향신료 부담 없음</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>5분 완조리</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>국산 새우·숙주 등 재료</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>진짜 팟타이 아닐 것</t>
@@ -2417,32 +2421,32 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>직접 만든다</t>
+          <t>냉동/밀키트</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>기존 방식 유지</t>
+          <t>가끔 산다</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2473,7 +2477,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>지인 소개</t>
+          <t>직장인 커뮤니티</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2498,17 +2502,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>있다</t>
+          <t>없다</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>먹어봤고 좋아한다</t>
+          <t>먹어봤고 보통이다</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>①향신료향 부담</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2516,7 +2520,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>향신료 부담 없음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2536,7 +2540,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>냉동/밀키트</t>
+          <t>이런 맛 안 찾음</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2566,7 +2570,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>가(T1·완성도)</t>
+          <t>나(T2·매실청)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2592,12 +2596,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>지인 소개</t>
+          <t>직장인 커뮤니티</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>35-39</t>
+          <t>40+</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2612,7 +2616,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0회</t>
+          <t>1-2회</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2622,16 +2626,16 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>⑥지금도 잘 먹음</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2640,7 +2644,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>외식 대비 가성비</t>
+          <t>매실청의 새콤한 맛</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2650,12 +2654,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>그렇다</t>
+          <t>아니다</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>이런 맛 안 찾음</t>
+          <t>배달·외식</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2665,7 +2669,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2691,17 +2695,17 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>확장세그</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2720,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>30-34</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2726,12 +2730,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0회</t>
+          <t>6+회</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2741,7 +2745,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2750,7 +2754,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2759,12 +2763,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>외식 대비 가성비</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2774,7 +2778,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>직접 만든다</t>
+          <t>냉동/밀키트</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2784,7 +2788,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2804,18 +2808,18 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>가(T1·완성도)</t>
+          <t>나(T2·매실청)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
-          <t>확장세그</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2835,7 +2839,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>40+</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2850,7 +2854,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>0회</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2869,31 +2873,31 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>매실청의 새콤한 맛</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>향신료 부담 없음</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>아니다</t>
+          <t>그렇다</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>안 먹거나 참는다</t>
+          <t>배달·외식</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2903,43 +2907,43 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>나(T2·매실청)</t>
+          <t>가(T1·완성도)</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
-          <t>타깃</t>
+          <t>확장세그</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>통과</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2953,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>지인 소개</t>
+          <t>직장인 커뮤니티</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2959,17 +2963,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>자영업·프리랜서</t>
+          <t>직장인</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1인가구</t>
+          <t>2인가구</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2979,7 +2983,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>먹어봤고 좋아한다</t>
+          <t>먹어봤고 보통이다</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2988,7 +2992,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2997,12 +3001,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>외식 대비 가성비</t>
+          <t>향신료 부담 없음</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3032,7 +3036,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3045,11 +3049,7 @@
           <t>가(T1·완성도)</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>뭐 5분이면 된다니 배달보단 낫겠죠</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>타깃</t>
@@ -3072,12 +3072,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>지인 소개</t>
+          <t>직장인 커뮤니티</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>40+</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3087,17 +3087,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>2인가구</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>없다</t>
+          <t>있다</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>국산 새우·숙주 등 재료</t>
+          <t>매실청의 새콤한 맛</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>안 먹거나 참는다</t>
+          <t>직접 만든다</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>가끔 산다</t>
+          <t>기존 방식 유지</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3168,15 +3168,19 @@
           <t>나(T2·매실청)</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>매실청이라니 맛이 상상돼서 진짜 팟타이일지 걱정이 좀 덜함</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3191,7 +3195,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>지인 소개</t>
+          <t>직장인 커뮤니티</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3201,17 +3205,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>자영업·프리랜서</t>
+          <t>직장인</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>2인가구</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3226,7 +3230,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>⑥지금도 잘 먹음</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -3234,17 +3238,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>매실청의 새콤한 맛</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>외식 대비 가성비</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>진짜 팟타이 아닐 것</t>
+          <t>양(300g) 부족</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3254,12 +3258,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>배달·외식</t>
+          <t>안 먹거나 참는다</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>가끔 산다</t>
+          <t>기존 방식 유지</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3269,12 +3273,12 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3284,22 +3288,22 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>나(T2·매실청)</t>
+          <t>가(T1·완성도)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>매실청이면 그래도 맛 걱정은 좀 덜하니까... 반신반의지만</t>
+          <t>뭐 5분이면 간편하니까 그게 낫죠</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3334,7 +3338,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>6+회</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3344,12 +3348,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>⑥지금도 잘 먹음</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -3357,17 +3361,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>외식 대비 가성비</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>5분 완조리</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>외식 대비 가성비</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3387,7 +3391,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3433,12 +3437,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>직장인 커뮤니티</t>
+          <t>지인 소개</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>30-34</t>
+          <t>40+</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3448,17 +3452,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>2인가구</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>있다</t>
+          <t>없다</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3486,7 +3490,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3496,12 +3500,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>안 먹거나 참는다</t>
+          <t>직접 만든다</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>꼭 산다</t>
+          <t>가끔 산다</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3531,17 +3535,17 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>나가서 사먹기 귀찮은데 5분이면 되니까 이게 낫네요</t>
+          <t>파는 데 찾기 귀찮았는데 집에서 5분이면 되니까요</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3561,12 +3565,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>25-29</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>직장인</t>
+          <t>자영업·프리랜서</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3576,17 +3580,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>있다</t>
+          <t>없다</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>먹어봤고 좋아한다</t>
+          <t>먹어봤고 보통이다</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3595,7 +3599,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3604,12 +3608,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>매실청의 새콤한 맛</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3619,12 +3623,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>직접 만든다</t>
+          <t>배달·외식</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>가끔 산다</t>
+          <t>기존 방식 유지</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3705,12 +3709,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>⑤단순 비선호</t>
+          <t>③접근성 부족</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -3728,7 +3732,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3738,7 +3742,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>직접 만든다</t>
+          <t>안 먹거나 참는다</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3753,12 +3757,12 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3794,17 +3798,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>지인 소개</t>
+          <t>직장인 커뮤니티</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>25-29</t>
+          <t>19-24</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>대학원생</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3814,7 +3818,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3-5회</t>
+          <t>1-2회</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3824,16 +3828,16 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>먹어봤고 좋아한다</t>
+          <t>먹어봤고 보통이다</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>⑥지금도 잘 먹음</t>
+          <t>⑤단순 비선호</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3842,7 +3846,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>외식 대비 가성비</t>
+          <t>매실청의 새콤한 맛</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3877,7 +3881,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3918,7 +3922,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>35-39</t>
+          <t>25-29</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3928,12 +3932,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1인가구</t>
+          <t>2인가구</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3-5회</t>
+          <t>6+회</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3952,7 +3956,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3966,7 +3970,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3976,7 +3980,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>냉동/밀키트</t>
+          <t>배달·외식</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3986,12 +3990,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4006,7 +4010,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>가(T1·완성도)</t>
+          <t>나(T2·매실청)</t>
         </is>
       </c>
       <c r="V30" t="inlineStr"/>
@@ -4037,7 +4041,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>40+</t>
+          <t>30-34</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4047,12 +4051,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>6+회</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4067,20 +4071,20 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>⑥지금도 잘 먹음</t>
+          <t>③접근성 부족</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>매실청의 새콤한 맛</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>향신료 부담 없음</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4095,48 +4099,48 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>배달·외식</t>
+          <t>안 먹거나 참는다</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>기존 방식 유지</t>
+          <t>가끔 산다</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>나(T2·매실청)</t>
+          <t>가(T1·완성도)</t>
         </is>
       </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4156,7 +4160,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>25-29</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4166,12 +4170,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2인가구</t>
+          <t>가족거주</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0회</t>
+          <t>1-2회</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4181,16 +4185,16 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>⑥지금도 잘 먹음</t>
+          <t>③접근성 부족</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4204,7 +4208,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4219,17 +4223,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>꼭 산다</t>
+          <t>기존 방식 유지</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4244,13 +4248,13 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>나(T2·매실청)</t>
+          <t>가(T1·완성도)</t>
         </is>
       </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
-          <t>확장세그</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4275,7 +4279,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>25-29</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4290,50 +4294,50 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>없다</t>
+          <t>있다</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>①향신료향 부담</t>
+          <t>⑥지금도 잘 먹음</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>매실청의 새콤한 맛</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>그렇다</t>
+          <t>아니다</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>이런 맛 안 찾음</t>
+          <t>안 먹거나 참는다</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4366,11 +4370,7 @@
           <t>나(T2·매실청)</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>고수 향 부담 없다는 거 하나는 끌리네요 (나머진 글쎄)</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>타깃</t>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>지인 소개</t>
+          <t>직장인 커뮤니티</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2인가구</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>④가격 부담</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>아니다</t>
+          <t>그렇다</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>기존 방식 유지</t>
+          <t>가끔 산다</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4489,7 +4489,11 @@
           <t>나(T2·매실청)</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>진짜 팟타이 맛일지가 젤 걱정인데 그걸 짚어주니 눈이 가긴 함</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>타깃</t>
@@ -4502,7 +4506,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>통과</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4516,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>직장인 커뮤니티</t>
+          <t>지인 소개</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19-24</t>
+          <t>30-34</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4527,7 +4531,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4547,7 +4551,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>⑥지금도 잘 먹음</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -4575,12 +4579,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>안 먹거나 참는다</t>
+          <t>직접 만든다</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>가끔 산다</t>
+          <t>꼭 산다</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -4611,12 +4615,12 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4641,12 +4645,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>직장인</t>
+          <t>자영업·프리랜서</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2인가구</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4656,7 +4660,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>없다</t>
+          <t>있다</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4670,7 +4674,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4689,7 +4693,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>아니다</t>
+          <t>그렇다</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -4699,27 +4703,27 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>기존 방식 유지</t>
+          <t>가끔 산다</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4740,7 +4744,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>통과</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4759,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>25-29</t>
+          <t>40+</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,7 +4802,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>국산 새우·숙주 등 재료</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4813,7 +4817,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>이런 맛 안 찾음</t>
+          <t>배달·외식</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4823,17 +4827,17 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -4869,7 +4873,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>지인 소개</t>
+          <t>직장인 커뮤니티</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4884,12 +4888,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4899,7 +4903,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4908,21 +4912,21 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t>5분 완조리</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>외식 대비 가성비</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>매실청의 새콤한 맛</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>진짜 팟타이 아닐 것</t>
+          <t>가격 걱정</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4932,7 +4936,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>이런 맛 안 찾음</t>
+          <t>냉동/밀키트</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4947,12 +4951,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -4962,18 +4966,18 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>나(T2·매실청)</t>
+          <t>가(T1·완성도)</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
-          <t>확장세그</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4993,12 +4997,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>30-34</t>
+          <t>25-29</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>직장인</t>
+          <t>자영업·프리랜서</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5008,12 +5012,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>6+회</t>
+          <t>1-2회</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>있다</t>
+          <t>없다</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5023,11 +5027,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>⑥지금도 잘 먹음</t>
+          <t>③접근성 부족</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5061,7 +5065,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -5084,11 +5088,7 @@
           <t>나(T2·매실청)</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>매실청으로 새콤함 잡았다는 게 궁금하긴 해요</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>타깃</t>
@@ -5111,12 +5111,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>지인 소개</t>
+          <t>직장인 커뮤니티</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>40+</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2인가구</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1-2회</t>
+          <t>6+회</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5141,16 +5141,16 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>먹어봤고 보통이다</t>
+          <t>먹어봤고 좋아한다</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>⑥지금도 잘 먹음</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>매실청의 새콤한 맛</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>진짜 팟타이 아닐 것</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>냉동/밀키트</t>
+          <t>배달·외식</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5204,10 +5204,14 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>가(T1·완성도)</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr"/>
+          <t>나(T2·매실청)</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>매실청으로 잡았다는 거 진짜 팟타이 맛일지 제일 궁금해요</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>타깃</t>
@@ -5235,7 +5239,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>25-29</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5245,17 +5249,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0회</t>
+          <t>6+회</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>있다</t>
+          <t>없다</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5269,16 +5273,16 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>매실청의 새콤한 맛</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -5308,7 +5312,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5323,22 +5327,18 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>나(T2·매실청)</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>고수 냄새 진짜 싫은데 그게 없다니까 이건 됨</t>
-        </is>
-      </c>
+          <t>가(T1·완성도)</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
-          <t>확장세그</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>40+</t>
+          <t>25-29</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>2인가구</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>외식 대비 가성비</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>그렇다</t>
+          <t>아니다</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>냉동/밀키트</t>
+          <t>이런 맛 안 찾음</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>기존 방식 유지</t>
+          <t>가끔 산다</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5452,17 +5452,17 @@
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -5472,17 +5472,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>직장인 커뮤니티</t>
+          <t>지인 소개</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>30-34</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>자영업·프리랜서</t>
+          <t>대학원생</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3-5회</t>
+          <t>1-2회</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>외식 대비 가성비</t>
+          <t>국산 새우·숙주 등 재료</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>기존 방식 유지</t>
+          <t>꼭 산다</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -5591,60 +5591,60 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>직장인 커뮤니티</t>
+          <t>지인 소개</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>25-29</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>직장인</t>
+          <t>자영업·프리랜서</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1인가구</t>
+          <t>2인가구</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0회</t>
+          <t>1-2회</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>있다</t>
+          <t>없다</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>먹어봤고 좋아한다</t>
+          <t>먹어봤고 보통이다</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>①향신료향 부담</t>
+          <t>③접근성 부족</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>향신료 부담 없음</t>
+          <t>5분 완조리</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>5분 완조리</t>
+          <t>매실청의 새콤한 맛</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>양(300g) 부족</t>
+          <t>맛 상상 안 됨</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>배달·외식</t>
+          <t>안 먹거나 참는다</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>꼭 산다</t>
+          <t>가끔 산다</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -5690,12 +5690,12 @@
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
-          <t>확장세그</t>
+          <t>타깃</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>35-39</t>
+          <t>40+</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2인가구</t>
+          <t>1인가구</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5749,21 +5749,21 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t>외식 대비 가성비</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>5분 완조리</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>향신료 부담 없음</t>
-        </is>
-      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>진짜 팟타이 아닐 것</t>
+          <t>양(300g) 부족</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>배달·외식</t>
+          <t>냉동/밀키트</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>가끔 산다</t>
+          <t>기존 방식 유지</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>안 산다</t>
+          <t>산다</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>집에서 딱 5분이면 되는 게 진짜 좋아요</t>
+          <t>어차피 자주 먹는 거 5분이면 편하긴 하죠</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>지인 소개</t>
+          <t>직장인 커뮤니티</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>30-34</t>
+          <t>40+</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5848,17 +5848,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>가족거주</t>
+          <t>2인가구</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0회</t>
+          <t>3-5회</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>없다</t>
+          <t>있다</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5868,15 +5868,15 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>③접근성 부족</t>
+          <t>⑥지금도 잘 먹음</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>매실청의 새콤한 맛</t>
+          <t>외식 대비 가성비</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>맛 상상 안 됨</t>
+          <t>양(300g) 부족</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>그렇다</t>
+          <t>아니다</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>산다</t>
+          <t>안 산다</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5932,15 +5932,618 @@
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
+          <t>타깃</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>직장인 커뮤니티</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>직장인</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>가족거주</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1-2회</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>없다</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>먹어봤고 보통이다</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>①향신료향 부담</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>향신료 부담 없음</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>5분 완조리</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>맛 상상 안 됨</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>아니다</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>배달·외식</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>기존 방식 유지</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>나(T2·매실청)</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>지인 소개</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>자영업·프리랜서</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>가족거주</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1-2회</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>없다</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>먹어봤고 보통이다</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>③접근성 부족</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>5분 완조리</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>국산 새우·숙주 등 재료</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>양(300g) 부족</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>그렇다</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>냉동/밀키트</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>꼭 산다</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>산다</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>가(T1·완성도)</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>그냥 간편한 게 제일 와닿아요</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>지인 소개</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>자영업·프리랜서</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1인가구</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>3-5회</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>없다</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>먹어봤고 좋아한다</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>③접근성 부족</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>4</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>5분 완조리</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>외식 대비 가성비</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>양(300g) 부족</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>그렇다</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>냉동/밀키트</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>가끔 산다</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>산다</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>가(T1·완성도)</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>타깃</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>직장인 커뮤니티</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>직장인</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1인가구</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>6+회</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>없다</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>먹어봤고 좋아한다</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>③접근성 부족</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>5분 완조리</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>외식 대비 가성비</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>양(300g) 부족</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>그렇다</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>안 먹거나 참는다</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>가끔 산다</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>산다</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>산다</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>가(T1·완성도)</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>혼자 살면 해먹기 귀찮은데 5분이면 되니까 딱 좋죠</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>타깃</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>지인 소개</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>19-24</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>가족거주</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0회</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>있다</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>먹어봤고 보통이다</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>③접근성 부족</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>5분 완조리</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>국산 새우·숙주 등 재료</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>맛 상상 안 됨</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>그렇다</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>배달·외식</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>가끔 산다</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>안 산다</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>가(T1·완성도)</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
           <t>확장세그</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>아니오</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>통과</t>
         </is>
